--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>70407540</v>
+        <v>77937.53</v>
       </c>
     </row>
     <row r="3">
@@ -626,17 +626,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>37160999.89</v>
+        <v>41135.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>586-215-CM26</t>
+          <t>3595-236-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -661,43 +661,43 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>63142199.68</v>
+        <v>38545.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5147-160-CM26</t>
+          <t>3637-159-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>69.251.500-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,28 +737,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>PENA SPOERER Y CIA S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.877.150-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>70434795.76000001</v>
+        <v>37182.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3153-167-CM26</t>
+          <t>1048-223-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -783,17 +783,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -809,17 +809,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>31403620.43</v>
+        <v>36838.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1431841-519-CM26</t>
+          <t>3561-226-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,28 +859,28 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.262.067-5</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>17481338</v>
+        <v>18247.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1048-223-CM26</t>
+          <t>5147-160-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,48 +900,48 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>33279234.17</v>
+        <v>77967.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3637-159-CM26</t>
+          <t>586-215-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -966,43 +966,43 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.251.500-5</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PENA SPOERER Y CIA S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.877.150-7</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>33590130</v>
+        <v>69895.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3595-236-CM26</t>
+          <t>3153-167-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1027,43 +1027,43 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>34821000.55</v>
+        <v>34762.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3561-226-CM26</t>
+          <t>4139-194-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,43 +1088,43 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.091.000-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE PALMILLA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>16484776.07</v>
+        <v>39425.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4139-194-CM26</t>
+          <t>3661-311-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,48 +1144,48 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.091.000-4</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PALMILLA</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35616224</v>
+        <v>23470.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3661-311-CM26</t>
+          <t>4316-25-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,53 +1200,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>21202632.22</v>
+        <v>19031.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4316-25-CM26</t>
+          <t>4121-53-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,43 +1271,43 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>17192599.97</v>
+        <v>69364.61</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4121-53-CM26</t>
+          <t>2436-650-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,43 +1332,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>62662903.38</v>
+        <v>14167.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3200-212-CM26</t>
+          <t>3712-361-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,43 +1393,43 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>20000000.37</v>
+        <v>44633.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2436-650-CM26</t>
+          <t>4042-123-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,43 +1454,43 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.220.402-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>Ilustre Municipalidad de Fresia - Salud</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12798549.96</v>
+        <v>38968.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3712-361-CM26</t>
+          <t>3200-212-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,43 +1515,43 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>40321484</v>
+        <v>22138.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4042-123-CM26</t>
+          <t>324-281-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,37 +1576,37 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.220.402-6</t>
+          <t>69.255.000-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>I MUNICIPALIDAD DE CERRILLOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>35203770</v>
+        <v>52246.83</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>24786728.96</v>
+        <v>27437.64</v>
       </c>
     </row>
     <row r="21">
@@ -1724,17 +1724,17 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>31616630.43</v>
+        <v>34997.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>324-281-CM26</t>
+          <t>3678-155-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,43 +1759,43 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.255.000-5</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CERRILLOS</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>47198970</v>
+        <v>72186.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3624-312-CM26</t>
+          <t>906973-28-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,48 +1815,48 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>65667884.24</v>
+        <v>61945.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3624-311-CM26</t>
+          <t>4051-114-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,37 +1881,37 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>24462158.84</v>
+        <v>41135.32</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>12787265.19</v>
+        <v>14154.85</v>
       </c>
     </row>
     <row r="26">
@@ -2029,17 +2029,17 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>12870800.81</v>
+        <v>14247.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>906973-28-CM26</t>
+          <t>3624-311-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,48 +2059,48 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>55960513.98</v>
+        <v>27078.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3678-155-CM26</t>
+          <t>3624-312-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,28 +2140,28 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>65212000</v>
+        <v>72690.97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4051-114-CM26</t>
+          <t>4414-752-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,17 +2186,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2212,17 +2212,17 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>37160999.89</v>
+        <v>54523.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4179-672-CM26</t>
+          <t>3014-167-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,48 +2242,48 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.081.600-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE COINCO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SKC Transportes S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.176.602-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>61182000.74</v>
+        <v>22987.66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3014-167-CM26</t>
+          <t>3117-778-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,48 +2303,48 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.081.600-8</t>
+          <t>61.102.006-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COINCO</t>
+          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SKC Transportes S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.176.602-3</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>20766690</v>
+        <v>18297.73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3117-778-CM26</t>
+          <t>3567-317-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2364,48 +2364,48 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.102.006-6</t>
+          <t>69.150.700-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>16529884.21</v>
+        <v>78885.42999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3567-317-CM26</t>
+          <t>324-289-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.150.700-9</t>
+          <t>69.255.000-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FLORIDA</t>
+          <t>I MUNICIPALIDAD DE CERRILLOS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2445,28 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>71263858.05</v>
+        <v>25439.45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>324-289-CM26</t>
+          <t>2997-66-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,43 +2491,43 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.255.000-5</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CERRILLOS</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22981598.92</v>
+        <v>29496.28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2997-66-CM26</t>
+          <t>4179-672-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,48 +2547,48 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26646480</v>
+        <v>67725.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4414-752-CM26</t>
+          <t>3820-514-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,53 +2603,53 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>49255290</v>
+        <v>32364.52</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3820-514-CM26</t>
+          <t>3573-46-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2669,48 +2669,48 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>29237600.28</v>
+        <v>42669.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3573-46-CM26</t>
+          <t>3820-518-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,53 +2725,53 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>38546767.98</v>
+        <v>70315.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3820-518-CM26</t>
+          <t>3568-415-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2791,48 +2791,48 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>63522200</v>
+        <v>64607.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3568-415-CM26</t>
+          <t>3723-58-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,43 +2857,43 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>58365600.37</v>
+        <v>49632.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5413-571-CM26</t>
+          <t>2674-509-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,53 +2908,53 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Guillermo Morales Ltda</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.564.810-0</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>32476171</v>
+        <v>36766.29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3723-58-CM26</t>
+          <t>3502-259-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,43 +2979,43 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>44837100.84</v>
+        <v>17771.27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2674-509-CM26</t>
+          <t>2436-705-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3035,48 +3035,48 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ COADIG LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>78.068.830-0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>33214090</v>
+        <v>42741.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3502-259-CM26</t>
+          <t>2337-55-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,43 +3101,43 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16054290</v>
+        <v>22297.04</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2436-705-CM26</t>
+          <t>1269-43-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,43 +3162,43 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ COADIG LIMITADA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.068.830-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>38612402.43</v>
+        <v>28194.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2337-55-CM26</t>
+          <t>2585-483-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,53 +3213,53 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>20142800.37</v>
+        <v>61996.23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1269-44-CM26</t>
+          <t>3693-105-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,53 +3274,53 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>GUILLERMO MORALES GROUP LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>78.027.627-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1153735</v>
+        <v>29634.47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1269-43-CM26</t>
+          <t>2404-799-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,43 +3345,43 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>77.262.067-5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>25470199.51</v>
+        <v>32616.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2585-483-CM26</t>
+          <t>3515-285-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,48 +3401,48 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>56006417.04</v>
+        <v>39122.88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3693-105-CM26</t>
+          <t>3887-225-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3467,43 +3467,43 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>GUILLERMO MORALES GROUP LIMITADA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.027.627-4</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>26771311</v>
+        <v>14647.21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2404-799-CM26</t>
+          <t>3416-328-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3523,48 +3523,48 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.101.017-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.262.067-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>29464876</v>
+        <v>73294.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3515-285-CM26</t>
+          <t>642028-37-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,53 +3579,53 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>35343000</v>
+        <v>30235.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3887-225-CM26</t>
+          <t>2713-684-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,53 +3640,53 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>13232058.63</v>
+        <v>45103.17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3416-328-CM26</t>
+          <t>2337-57-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,53 +3701,53 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.101.017-6</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>66213504</v>
+        <v>31415.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>642028-37-CM26</t>
+          <t>2345-261-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3767,17 +3767,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,28 +3787,28 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>27314099.75</v>
+        <v>603.08</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2713-684-CM26</t>
+          <t>2345-260-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3828,48 +3828,48 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>40745500.04</v>
+        <v>27885.14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2345-261-CM26</t>
+          <t>2429-733-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,53 +3884,53 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>544816</v>
+        <v>29744.15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2345-260-CM26</t>
+          <t>2429-734-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,43 +3955,43 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>25190999.33</v>
+        <v>754.45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2337-57-CM26</t>
+          <t>2963-69-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,43 +4016,43 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.072.400-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>28380000.6</v>
+        <v>40571.88</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2429-733-CM26</t>
+          <t>1426095-155-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,53 +4067,53 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>26870399.92</v>
+        <v>30100.91</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2429-734-CM26</t>
+          <t>1426095-156-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,43 +4138,43 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>681560</v>
+        <v>1249.55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2963-69-CM26</t>
+          <t>2322-454-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,43 +4199,43 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>36652000</v>
+        <v>37925.49</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2322-454-CM26</t>
+          <t>2322-455-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4275,28 +4275,28 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>34261290</v>
+        <v>16182.26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2322-455-CM26</t>
+          <t>941739-50-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,43 +4321,43 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>14618800.14</v>
+        <v>33840.08</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1426095-155-CM26</t>
+          <t>3661-357-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,53 +4372,53 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>27192690</v>
+        <v>11800.4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1426095-156-CM26</t>
+          <t>3661-358-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,37 +4443,37 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1128828</v>
+        <v>396.28</v>
       </c>
     </row>
     <row r="67">
@@ -4530,17 +4530,17 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>23015790</v>
+        <v>25477.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>941739-50-CM26</t>
+          <t>1456836-7-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4565,43 +4565,43 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>61.981.410-K</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>30570600.2</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3661-357-CM26</t>
+          <t>4314-256-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,53 +4616,53 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>10660299.65</v>
+        <v>33208.46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3661-358-CM26</t>
+          <t>1180825-16-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,53 +4677,53 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>357997</v>
+        <v>48407.97</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1456836-7-CM26</t>
+          <t>1286987-18-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,220 +4748,37 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.981.410-K</t>
+          <t>65.797.310-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
+          <t>Corporación Municipal de Deportes y Recreación Coy</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1304486</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>4314-256-CM26</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>69.110.300-5</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>29999999.96</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>1180825-16-CM26</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>61.606.400-2</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>43731000.6</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>1286987-18-CM26</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>65.797.310-6</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Corporación Municipal de Deportes y Recreación Coy</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="n">
-        <v>71263858.05</v>
+        <v>78885.42999999999</v>
       </c>
     </row>
   </sheetData>
